--- a/netlify/template-files/data-inventory-map.xlsx
+++ b/netlify/template-files/data-inventory-map.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README &amp; Legend" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Inventory Map" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dropdown Reference" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version Control" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data Inventory Map'!$A$1:$AF$29</definedName>
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -119,8 +119,12 @@
       <family val="2"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -169,6 +173,11 @@
         <bgColor rgb="FF333399"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B21B6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -204,7 +213,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -356,6 +365,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="B2:D43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="30" min="1" max="1"/>
@@ -691,7 +701,6 @@
     <col width="18" customWidth="1" style="30" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="22.05" customHeight="1" s="31">
       <c r="B2" s="32" t="inlineStr">
         <is>
@@ -706,7 +715,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="46.25" customHeight="1" s="31">
       <c r="B5" s="34" t="inlineStr">
         <is>
@@ -720,7 +728,6 @@
       </c>
       <c r="D5" s="34" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="31">
       <c r="B7" s="34" t="inlineStr">
         <is>
@@ -904,8 +911,6 @@
       <c r="B27" s="39" t="n"/>
       <c r="C27" s="37" t="n"/>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="31">
       <c r="B30" s="34" t="n"/>
       <c r="C30" s="34" t="n"/>
@@ -943,8 +948,6 @@
       <c r="B38" s="40" t="n"/>
       <c r="C38" s="41" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="31">
       <c r="B41" s="42" t="n"/>
     </row>
@@ -2941,104 +2944,75 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="30" min="1" max="1"/>
-    <col width="14" customWidth="1" style="30" min="2" max="2"/>
-    <col width="20" customWidth="1" style="30" min="3" max="3"/>
-    <col width="22" customWidth="1" style="30" min="4" max="4"/>
-    <col width="110" customWidth="1" style="30" min="5" max="5"/>
-    <col width="26" customWidth="1" style="30" min="6" max="6"/>
+    <col width="24" customWidth="1" style="31" min="1" max="1"/>
+    <col width="24" customWidth="1" style="31" min="2" max="2"/>
+    <col width="24" customWidth="1" style="31" min="3" max="3"/>
+    <col width="24" customWidth="1" style="31" min="4" max="4"/>
+    <col width="24" customWidth="1" style="31" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="31">
-      <c r="A1" s="49" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="51" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="D1" s="49" t="inlineStr">
-        <is>
-          <t>Reviewer / Approver</t>
-        </is>
-      </c>
-      <c r="E1" s="49" t="inlineStr">
-        <is>
-          <t>Change Summary</t>
-        </is>
-      </c>
-      <c r="F1" s="49" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="31">
-      <c r="A2" s="37" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B2" s="37" t="inlineStr">
-        <is>
-          <t>[YYYY-MM-DD]</t>
-        </is>
-      </c>
-      <c r="C2" s="37" t="inlineStr">
-        <is>
-          <t>[Author role]</t>
-        </is>
-      </c>
-      <c r="D2" s="37" t="inlineStr">
-        <is>
-          <t>[Reviewer / Approver]</t>
-        </is>
-      </c>
-      <c r="E2" s="37" t="inlineStr">
-        <is>
-          <t>Initial version</t>
-        </is>
-      </c>
-      <c r="F2" s="37" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="150" customHeight="1" s="31">
-      <c r="A3" s="37" t="n"/>
-      <c r="B3" s="37" t="n"/>
-      <c r="C3" s="37" t="n"/>
-      <c r="D3" s="37" t="n"/>
-      <c r="E3" s="37" t="n"/>
-      <c r="F3" s="37" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="31">
-      <c r="A4" s="37" t="n"/>
-      <c r="B4" s="37" t="n"/>
-      <c r="C4" s="37" t="n"/>
-      <c r="D4" s="37" t="n"/>
-      <c r="E4" s="37" t="n"/>
-      <c r="F4" s="37" t="n"/>
+      <c r="C1" s="51" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="51" t="inlineStr">
+        <is>
+          <t>Written by</t>
+        </is>
+      </c>
+      <c r="E1" s="51" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[TODAYS DATE]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial Version</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[Name]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[Name]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>